--- a/artfynd/A 32236-2025 artfynd.xlsx
+++ b/artfynd/A 32236-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>126837938</v>
       </c>
       <c r="B3" t="n">
-        <v>98279</v>
+        <v>98354</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>126837939</v>
       </c>
       <c r="B4" t="n">
-        <v>98279</v>
+        <v>98354</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>126837933</v>
       </c>
       <c r="B5" t="n">
-        <v>98384</v>
+        <v>98459</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
         <v>126837955</v>
       </c>
       <c r="B7" t="n">
-        <v>98395</v>
+        <v>98470</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>126837968</v>
       </c>
       <c r="B8" t="n">
-        <v>98267</v>
+        <v>98342</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>126837952</v>
       </c>
       <c r="B9" t="n">
-        <v>98395</v>
+        <v>98470</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>126837971</v>
       </c>
       <c r="B10" t="n">
-        <v>100543</v>
+        <v>100618</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>126837957</v>
       </c>
       <c r="B11" t="n">
-        <v>98395</v>
+        <v>98470</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>126837953</v>
       </c>
       <c r="B12" t="n">
-        <v>98395</v>
+        <v>98470</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1771,10 +1771,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126837935</v>
+        <v>126837965</v>
       </c>
       <c r="B13" t="n">
-        <v>103803</v>
+        <v>95293</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1782,21 +1782,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222412</v>
+        <v>2387</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1806,10 +1806,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>514331</v>
+        <v>514459</v>
       </c>
       <c r="R13" t="n">
-        <v>6757740</v>
+        <v>6757797</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1868,10 +1868,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126837965</v>
+        <v>126837935</v>
       </c>
       <c r="B14" t="n">
-        <v>95218</v>
+        <v>103878</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1879,21 +1879,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2387</v>
+        <v>222412</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1903,10 +1903,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>514459</v>
+        <v>514331</v>
       </c>
       <c r="R14" t="n">
-        <v>6757797</v>
+        <v>6757740</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1968,7 +1968,7 @@
         <v>126837932</v>
       </c>
       <c r="B15" t="n">
-        <v>98384</v>
+        <v>98459</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         <v>126837966</v>
       </c>
       <c r="B16" t="n">
-        <v>80043</v>
+        <v>80074</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>126837970</v>
       </c>
       <c r="B17" t="n">
-        <v>100543</v>
+        <v>100618</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 32236-2025 artfynd.xlsx
+++ b/artfynd/A 32236-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>126837938</v>
       </c>
       <c r="B3" t="n">
-        <v>98354</v>
+        <v>98360</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>126837939</v>
       </c>
       <c r="B4" t="n">
-        <v>98354</v>
+        <v>98360</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>126837933</v>
       </c>
       <c r="B5" t="n">
-        <v>98459</v>
+        <v>98465</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
         <v>126837955</v>
       </c>
       <c r="B7" t="n">
-        <v>98470</v>
+        <v>98476</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>126837968</v>
       </c>
       <c r="B8" t="n">
-        <v>98342</v>
+        <v>98348</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>126837952</v>
       </c>
       <c r="B9" t="n">
-        <v>98470</v>
+        <v>98476</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>126837971</v>
       </c>
       <c r="B10" t="n">
-        <v>100618</v>
+        <v>100624</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>126837957</v>
       </c>
       <c r="B11" t="n">
-        <v>98470</v>
+        <v>98476</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>126837953</v>
       </c>
       <c r="B12" t="n">
-        <v>98470</v>
+        <v>98476</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>126837965</v>
       </c>
       <c r="B13" t="n">
-        <v>95293</v>
+        <v>95299</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>126837935</v>
       </c>
       <c r="B14" t="n">
-        <v>103878</v>
+        <v>103884</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>126837932</v>
       </c>
       <c r="B15" t="n">
-        <v>98459</v>
+        <v>98465</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         <v>126837966</v>
       </c>
       <c r="B16" t="n">
-        <v>80074</v>
+        <v>80077</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>126837970</v>
       </c>
       <c r="B17" t="n">
-        <v>100618</v>
+        <v>100624</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 32236-2025 artfynd.xlsx
+++ b/artfynd/A 32236-2025 artfynd.xlsx
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126837938</v>
+        <v>126837939</v>
       </c>
       <c r="B3" t="n">
-        <v>98360</v>
+        <v>98361</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514373</v>
+        <v>514483</v>
       </c>
       <c r="R3" t="n">
-        <v>6757389</v>
+        <v>6757744</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -893,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126837939</v>
+        <v>126837938</v>
       </c>
       <c r="B4" t="n">
-        <v>98360</v>
+        <v>98361</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>514483</v>
+        <v>514373</v>
       </c>
       <c r="R4" t="n">
-        <v>6757744</v>
+        <v>6757389</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +993,7 @@
         <v>126837933</v>
       </c>
       <c r="B5" t="n">
-        <v>98465</v>
+        <v>98466</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
         <v>126837955</v>
       </c>
       <c r="B7" t="n">
-        <v>98476</v>
+        <v>98477</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>126837968</v>
       </c>
       <c r="B8" t="n">
-        <v>98348</v>
+        <v>98349</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>126837952</v>
       </c>
       <c r="B9" t="n">
-        <v>98476</v>
+        <v>98477</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>126837971</v>
       </c>
       <c r="B10" t="n">
-        <v>100624</v>
+        <v>100625</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>126837957</v>
       </c>
       <c r="B11" t="n">
-        <v>98476</v>
+        <v>98477</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>126837953</v>
       </c>
       <c r="B12" t="n">
-        <v>98476</v>
+        <v>98477</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1771,10 +1771,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126837965</v>
+        <v>126837935</v>
       </c>
       <c r="B13" t="n">
-        <v>95299</v>
+        <v>103885</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1782,21 +1782,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2387</v>
+        <v>222412</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1806,10 +1806,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>514459</v>
+        <v>514331</v>
       </c>
       <c r="R13" t="n">
-        <v>6757797</v>
+        <v>6757740</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1868,10 +1868,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126837935</v>
+        <v>126837965</v>
       </c>
       <c r="B14" t="n">
-        <v>103884</v>
+        <v>95300</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1879,21 +1879,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222412</v>
+        <v>2387</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1903,10 +1903,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>514331</v>
+        <v>514459</v>
       </c>
       <c r="R14" t="n">
-        <v>6757740</v>
+        <v>6757797</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1968,7 +1968,7 @@
         <v>126837932</v>
       </c>
       <c r="B15" t="n">
-        <v>98465</v>
+        <v>98466</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>126837970</v>
       </c>
       <c r="B17" t="n">
-        <v>100624</v>
+        <v>100625</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 32236-2025 artfynd.xlsx
+++ b/artfynd/A 32236-2025 artfynd.xlsx
@@ -1771,10 +1771,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126837935</v>
+        <v>126837965</v>
       </c>
       <c r="B13" t="n">
-        <v>103885</v>
+        <v>95300</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1782,21 +1782,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222412</v>
+        <v>2387</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1806,10 +1806,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>514331</v>
+        <v>514459</v>
       </c>
       <c r="R13" t="n">
-        <v>6757740</v>
+        <v>6757797</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1868,10 +1868,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126837965</v>
+        <v>126837935</v>
       </c>
       <c r="B14" t="n">
-        <v>95300</v>
+        <v>103885</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1879,21 +1879,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2387</v>
+        <v>222412</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1903,10 +1903,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>514459</v>
+        <v>514331</v>
       </c>
       <c r="R14" t="n">
-        <v>6757797</v>
+        <v>6757740</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 32236-2025 artfynd.xlsx
+++ b/artfynd/A 32236-2025 artfynd.xlsx
@@ -796,7 +796,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126837939</v>
+        <v>126837938</v>
       </c>
       <c r="B3" t="n">
         <v>98361</v>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514483</v>
+        <v>514373</v>
       </c>
       <c r="R3" t="n">
-        <v>6757744</v>
+        <v>6757389</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -893,7 +893,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126837938</v>
+        <v>126837939</v>
       </c>
       <c r="B4" t="n">
         <v>98361</v>
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>514373</v>
+        <v>514483</v>
       </c>
       <c r="R4" t="n">
-        <v>6757389</v>
+        <v>6757744</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 32236-2025 artfynd.xlsx
+++ b/artfynd/A 32236-2025 artfynd.xlsx
@@ -1087,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126837959</v>
+        <v>126837955</v>
       </c>
       <c r="B6" t="n">
-        <v>8447</v>
+        <v>98477</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1098,21 +1098,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>219874</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1122,10 +1122,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>514579</v>
+        <v>514543</v>
       </c>
       <c r="R6" t="n">
-        <v>6757622</v>
+        <v>6757666</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1184,10 +1184,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126837955</v>
+        <v>126837959</v>
       </c>
       <c r="B7" t="n">
-        <v>98477</v>
+        <v>8447</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1195,21 +1195,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219874</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>514543</v>
+        <v>514579</v>
       </c>
       <c r="R7" t="n">
-        <v>6757666</v>
+        <v>6757622</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 32236-2025 artfynd.xlsx
+++ b/artfynd/A 32236-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>126837938</v>
       </c>
       <c r="B3" t="n">
-        <v>98361</v>
+        <v>98365</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>126837939</v>
       </c>
       <c r="B4" t="n">
-        <v>98361</v>
+        <v>98365</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>126837933</v>
       </c>
       <c r="B5" t="n">
-        <v>98466</v>
+        <v>98470</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1087,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126837955</v>
+        <v>126837959</v>
       </c>
       <c r="B6" t="n">
-        <v>98477</v>
+        <v>8450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1098,21 +1098,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219874</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1122,10 +1122,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>514543</v>
+        <v>514579</v>
       </c>
       <c r="R6" t="n">
-        <v>6757666</v>
+        <v>6757622</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1184,10 +1184,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126837959</v>
+        <v>126837955</v>
       </c>
       <c r="B7" t="n">
-        <v>8447</v>
+        <v>98481</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1195,21 +1195,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>219874</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>514579</v>
+        <v>514543</v>
       </c>
       <c r="R7" t="n">
-        <v>6757622</v>
+        <v>6757666</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1284,7 +1284,7 @@
         <v>126837968</v>
       </c>
       <c r="B8" t="n">
-        <v>98349</v>
+        <v>98353</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>126837952</v>
       </c>
       <c r="B9" t="n">
-        <v>98477</v>
+        <v>98481</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>126837971</v>
       </c>
       <c r="B10" t="n">
-        <v>100625</v>
+        <v>100629</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>126837957</v>
       </c>
       <c r="B11" t="n">
-        <v>98477</v>
+        <v>98481</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>126837953</v>
       </c>
       <c r="B12" t="n">
-        <v>98477</v>
+        <v>98481</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>126837965</v>
       </c>
       <c r="B13" t="n">
-        <v>95300</v>
+        <v>95304</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>126837935</v>
       </c>
       <c r="B14" t="n">
-        <v>103885</v>
+        <v>103891</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>126837932</v>
       </c>
       <c r="B15" t="n">
-        <v>98466</v>
+        <v>98470</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         <v>126837966</v>
       </c>
       <c r="B16" t="n">
-        <v>80077</v>
+        <v>80081</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>126837970</v>
       </c>
       <c r="B17" t="n">
-        <v>100625</v>
+        <v>100629</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 32236-2025 artfynd.xlsx
+++ b/artfynd/A 32236-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>126837938</v>
       </c>
       <c r="B3" t="n">
-        <v>98365</v>
+        <v>98366</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>126837939</v>
       </c>
       <c r="B4" t="n">
-        <v>98365</v>
+        <v>98366</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>126837933</v>
       </c>
       <c r="B5" t="n">
-        <v>98470</v>
+        <v>98471</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
         <v>126837955</v>
       </c>
       <c r="B7" t="n">
-        <v>98481</v>
+        <v>98482</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>126837968</v>
       </c>
       <c r="B8" t="n">
-        <v>98353</v>
+        <v>98354</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>126837952</v>
       </c>
       <c r="B9" t="n">
-        <v>98481</v>
+        <v>98482</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>126837971</v>
       </c>
       <c r="B10" t="n">
-        <v>100629</v>
+        <v>100630</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>126837957</v>
       </c>
       <c r="B11" t="n">
-        <v>98481</v>
+        <v>98482</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>126837953</v>
       </c>
       <c r="B12" t="n">
-        <v>98481</v>
+        <v>98482</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>126837935</v>
       </c>
       <c r="B14" t="n">
-        <v>103891</v>
+        <v>103893</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>126837932</v>
       </c>
       <c r="B15" t="n">
-        <v>98470</v>
+        <v>98471</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>126837970</v>
       </c>
       <c r="B17" t="n">
-        <v>100629</v>
+        <v>100630</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 32236-2025 artfynd.xlsx
+++ b/artfynd/A 32236-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>126837938</v>
       </c>
       <c r="B3" t="n">
-        <v>98366</v>
+        <v>98354</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>126837939</v>
       </c>
       <c r="B4" t="n">
-        <v>98366</v>
+        <v>98354</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>126837933</v>
       </c>
       <c r="B5" t="n">
-        <v>98471</v>
+        <v>98459</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>126837959</v>
       </c>
       <c r="B6" t="n">
-        <v>8450</v>
+        <v>8447</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
         <v>126837955</v>
       </c>
       <c r="B7" t="n">
-        <v>98482</v>
+        <v>98470</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>126837968</v>
       </c>
       <c r="B8" t="n">
-        <v>98354</v>
+        <v>98342</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>126837952</v>
       </c>
       <c r="B9" t="n">
-        <v>98482</v>
+        <v>98470</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>126837971</v>
       </c>
       <c r="B10" t="n">
-        <v>100630</v>
+        <v>100618</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>126837957</v>
       </c>
       <c r="B11" t="n">
-        <v>98482</v>
+        <v>98470</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>126837953</v>
       </c>
       <c r="B12" t="n">
-        <v>98482</v>
+        <v>98470</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>126837965</v>
       </c>
       <c r="B13" t="n">
-        <v>95304</v>
+        <v>95293</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>126837935</v>
       </c>
       <c r="B14" t="n">
-        <v>103893</v>
+        <v>103878</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>126837932</v>
       </c>
       <c r="B15" t="n">
-        <v>98471</v>
+        <v>98459</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         <v>126837966</v>
       </c>
       <c r="B16" t="n">
-        <v>80081</v>
+        <v>80074</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>126837970</v>
       </c>
       <c r="B17" t="n">
-        <v>100630</v>
+        <v>100618</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 32236-2025 artfynd.xlsx
+++ b/artfynd/A 32236-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>126837938</v>
       </c>
       <c r="B3" t="n">
-        <v>98354</v>
+        <v>98366</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>126837939</v>
       </c>
       <c r="B4" t="n">
-        <v>98354</v>
+        <v>98366</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>126837933</v>
       </c>
       <c r="B5" t="n">
-        <v>98459</v>
+        <v>98471</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>126837959</v>
       </c>
       <c r="B6" t="n">
-        <v>8447</v>
+        <v>8450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
         <v>126837955</v>
       </c>
       <c r="B7" t="n">
-        <v>98470</v>
+        <v>98482</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>126837968</v>
       </c>
       <c r="B8" t="n">
-        <v>98342</v>
+        <v>98354</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>126837952</v>
       </c>
       <c r="B9" t="n">
-        <v>98470</v>
+        <v>98482</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>126837971</v>
       </c>
       <c r="B10" t="n">
-        <v>100618</v>
+        <v>100630</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>126837957</v>
       </c>
       <c r="B11" t="n">
-        <v>98470</v>
+        <v>98482</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>126837953</v>
       </c>
       <c r="B12" t="n">
-        <v>98470</v>
+        <v>98482</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>126837965</v>
       </c>
       <c r="B13" t="n">
-        <v>95293</v>
+        <v>95304</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>126837935</v>
       </c>
       <c r="B14" t="n">
-        <v>103878</v>
+        <v>103893</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>126837932</v>
       </c>
       <c r="B15" t="n">
-        <v>98459</v>
+        <v>98471</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         <v>126837966</v>
       </c>
       <c r="B16" t="n">
-        <v>80074</v>
+        <v>80081</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>126837970</v>
       </c>
       <c r="B17" t="n">
-        <v>100618</v>
+        <v>100630</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
